--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -320,7 +320,7 @@
     <t>HospitalLocation44.Institution</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Country779004)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Institution4)
 </t>
   </si>
   <si>
@@ -637,7 +637,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="60.2578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="56.421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -244,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>HospitalLocation44.Service</t>
+    <t>HospitalLocation44.service</t>
   </si>
   <si>
     <t>1</t>
@@ -254,77 +257,77 @@
 </t>
   </si>
   <si>
-    <t>SERVICE (9)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.StopCodeNumber</t>
-  </si>
-  <si>
-    <t>STOP CODE NUMBER (8)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.CreditStopCode</t>
-  </si>
-  <si>
-    <t>CREDIT STOP CODE (2503)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.Type</t>
-  </si>
-  <si>
-    <t>TYPE (2)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.Ien</t>
-  </si>
-  <si>
-    <t>IEN (.001)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.Name</t>
-  </si>
-  <si>
-    <t>NAME (.01)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.Abbreviation</t>
-  </si>
-  <si>
-    <t>ABBREVIATION (1)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.Synonym</t>
-  </si>
-  <si>
-    <t>SYNONYM (13)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.PatientFriendlyName</t>
-  </si>
-  <si>
-    <t>PATIENT FRIENDLY NAME (60)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.Telephone</t>
-  </si>
-  <si>
-    <t>TELEPHONE (99)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.PhysicalLocation</t>
-  </si>
-  <si>
-    <t>PHYSICAL LOCATION (10)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.Institution</t>
+    <t>SERVICE (-9)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.stopCodeNumber</t>
+  </si>
+  <si>
+    <t>STOP CODE NUMBER (-8)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.creditStopCode</t>
+  </si>
+  <si>
+    <t>CREDIT STOP CODE (-2503)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.type</t>
+  </si>
+  <si>
+    <t>TYPE (-2)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.ien</t>
+  </si>
+  <si>
+    <t>IEN (-.001)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.name</t>
+  </si>
+  <si>
+    <t>NAME (-.01)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.abbreviation</t>
+  </si>
+  <si>
+    <t>ABBREVIATION (-1)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.synonym</t>
+  </si>
+  <si>
+    <t>SYNONYM (-13)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.patientFriendlyName</t>
+  </si>
+  <si>
+    <t>PATIENT FRIENDLY NAME (-60)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.telephone</t>
+  </si>
+  <si>
+    <t>TELEPHONE (-99)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.physicalLocation</t>
+  </si>
+  <si>
+    <t>PHYSICAL LOCATION (-10)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.institution</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Institution4)
 </t>
   </si>
   <si>
-    <t>INSTITUTION (3)</t>
+    <t>INSTITUTION (-3)</t>
   </si>
 </sst>
 </file>
@@ -555,39 +558,41 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -595,26 +600,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -627,8 +632,8 @@
   <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.46484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.46484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.5234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.5234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -658,7 +663,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.46484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.5234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -666,112 +671,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
@@ -783,1293 +788,1295 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="M2" s="2"/>
+      <c r="M2" t="s" s="2">
+        <v>22</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="107">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,14 +253,24 @@
     <t>1</t>
   </si>
   <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>SERVICE (-9)</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFLocationStatus-vista</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.stopCodeNumber</t>
+  </si>
+  <si>
     <t xml:space="preserve">Element
 </t>
-  </si>
-  <si>
-    <t>SERVICE (-9)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.stopCodeNumber</t>
   </si>
   <si>
     <t>STOP CODE NUMBER (-8)</t>
@@ -657,7 +667,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.33984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -940,13 +950,11 @@
         <v>72</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y3" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>72</v>
@@ -981,10 +989,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1007,13 +1015,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1064,7 +1072,7 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>
@@ -1081,10 +1089,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1107,13 +1115,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1164,7 +1172,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1181,10 +1189,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1207,13 +1215,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1264,7 +1272,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1281,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1307,13 +1315,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1364,7 +1372,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1381,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1407,13 +1415,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1464,7 +1472,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1481,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1507,13 +1515,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1564,7 +1572,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1581,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1607,13 +1615,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1664,7 +1672,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1681,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1707,13 +1715,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1764,7 +1772,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1781,10 +1789,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1807,13 +1815,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1864,7 +1872,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1881,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1907,13 +1915,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1964,7 +1972,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -1981,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2007,13 +2015,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2064,7 +2072,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>-</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file HOSPITAL LOCATION (44)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,7 +260,7 @@
     <t>SERVICE (-9)</t>
   </si>
   <si>
-    <t>example</t>
+    <t>preferred</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/VSVFLocationStatus-vista</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,24 +253,14 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>SERVICE (-9)</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLocationStatus-vista</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.stopCodeNumber</t>
-  </si>
-  <si>
     <t xml:space="preserve">Element
 </t>
+  </si>
+  <si>
+    <t>SERVICE (-9)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.stopCodeNumber</t>
   </si>
   <si>
     <t>STOP CODE NUMBER (-8)</t>
@@ -667,7 +657,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="49.33984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -950,11 +940,13 @@
         <v>72</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y3" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y3" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z3" t="s" s="2">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>72</v>
@@ -989,10 +981,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1015,13 +1007,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1072,7 +1064,7 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>
@@ -1089,10 +1081,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1115,13 +1107,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1172,7 +1164,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1189,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1215,13 +1207,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1272,7 +1264,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1289,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1315,13 +1307,13 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1372,7 +1364,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1389,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1415,13 +1407,13 @@
         <v>72</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1472,7 +1464,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1489,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1515,13 +1507,13 @@
         <v>72</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1572,7 +1564,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1589,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1615,13 +1607,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1672,7 +1664,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1689,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1715,13 +1707,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1772,7 +1764,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1789,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1815,13 +1807,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1872,7 +1864,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1889,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1915,13 +1907,13 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1972,7 +1964,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -1989,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2015,13 +2007,13 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2072,7 +2064,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the Logical Model for the mapped parts of the VistA file HOSPITAL LOCATION (44)</t>
+    <t>This StructureDefinition contains the Logical Model for the mapped parts of the source HOSPITAL LOCATION (44)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="107">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>HospitalLocation44.service</t>
+    <t>HospitalLocation44.name</t>
   </si>
   <si>
     <t>1</t>
@@ -257,6 +257,22 @@
 </t>
   </si>
   <si>
+    <t>NAME (-.01)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Provider441)
+</t>
+  </si>
+  <si>
+    <t>PROVIDER (-2600)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.service</t>
+  </si>
+  <si>
     <t>SERVICE (-9)</t>
   </si>
   <si>
@@ -282,12 +298,6 @@
   </si>
   <si>
     <t>IEN (-.001)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.name</t>
-  </si>
-  <si>
-    <t>NAME (-.01)</t>
   </si>
   <si>
     <t>HospitalLocation44.abbreviation</t>
@@ -629,7 +639,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.5234375" customWidth="true" bestFit="true"/>
@@ -642,7 +652,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="56.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="57.09765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1007,13 +1017,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1081,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1110,10 +1120,10 @@
         <v>79</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1164,7 +1174,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1181,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1210,10 +1220,10 @@
         <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1264,7 +1274,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1281,10 +1291,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1310,10 +1320,10 @@
         <v>79</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1364,7 +1374,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1381,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1410,10 +1420,10 @@
         <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1464,7 +1474,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1481,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1510,10 +1520,10 @@
         <v>79</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1564,7 +1574,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1610,10 +1620,10 @@
         <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1664,7 +1674,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1681,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1710,10 +1720,10 @@
         <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1764,7 +1774,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1781,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1810,10 +1820,10 @@
         <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1864,7 +1874,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1881,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1910,10 +1920,10 @@
         <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1964,7 +1974,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -1981,10 +1991,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2007,7 +2017,7 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>103</v>
@@ -2064,7 +2074,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
@@ -2076,6 +2086,106 @@
         <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>HospitalLocation44.name</t>
+    <t>HospitalLocation44.service</t>
   </si>
   <si>
     <t>1</t>
@@ -257,7 +257,77 @@
 </t>
   </si>
   <si>
+    <t>SERVICE (-9)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.stopCodeNumber</t>
+  </si>
+  <si>
+    <t>STOP CODE NUMBER (-8)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.creditStopCode</t>
+  </si>
+  <si>
+    <t>CREDIT STOP CODE (-2503)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.type</t>
+  </si>
+  <si>
+    <t>TYPE (-2)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.ien</t>
+  </si>
+  <si>
+    <t>IEN (-.001)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.name</t>
+  </si>
+  <si>
     <t>NAME (-.01)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.abbreviation</t>
+  </si>
+  <si>
+    <t>ABBREVIATION (-1)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.synonym</t>
+  </si>
+  <si>
+    <t>SYNONYM (-13)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.patientFriendlyName</t>
+  </si>
+  <si>
+    <t>PATIENT FRIENDLY NAME (-60)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.telephone</t>
+  </si>
+  <si>
+    <t>TELEPHONE (-99)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.physicalLocation</t>
+  </si>
+  <si>
+    <t>PHYSICAL LOCATION (-10)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.institution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Institution4)
+</t>
+  </si>
+  <si>
+    <t>INSTITUTION (-3)</t>
   </si>
   <si>
     <t>HospitalLocation44.provider</t>
@@ -268,76 +338,6 @@
   </si>
   <si>
     <t>PROVIDER (-2600)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.service</t>
-  </si>
-  <si>
-    <t>SERVICE (-9)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.stopCodeNumber</t>
-  </si>
-  <si>
-    <t>STOP CODE NUMBER (-8)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.creditStopCode</t>
-  </si>
-  <si>
-    <t>CREDIT STOP CODE (-2503)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.type</t>
-  </si>
-  <si>
-    <t>TYPE (-2)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.ien</t>
-  </si>
-  <si>
-    <t>IEN (-.001)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.abbreviation</t>
-  </si>
-  <si>
-    <t>ABBREVIATION (-1)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.synonym</t>
-  </si>
-  <si>
-    <t>SYNONYM (-13)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.patientFriendlyName</t>
-  </si>
-  <si>
-    <t>PATIENT FRIENDLY NAME (-60)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.telephone</t>
-  </si>
-  <si>
-    <t>TELEPHONE (-99)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.physicalLocation</t>
-  </si>
-  <si>
-    <t>PHYSICAL LOCATION (-10)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.institution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Institution4)
-</t>
-  </si>
-  <si>
-    <t>INSTITUTION (-3)</t>
   </si>
 </sst>
 </file>
@@ -1017,13 +1017,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="L4" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1120,10 +1120,10 @@
         <v>79</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1174,7 +1174,7 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1191,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1220,10 +1220,10 @@
         <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1274,7 +1274,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1320,10 +1320,10 @@
         <v>79</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1374,7 +1374,7 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1420,10 +1420,10 @@
         <v>79</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1474,7 +1474,7 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1520,10 +1520,10 @@
         <v>79</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1574,7 +1574,7 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1591,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1620,10 +1620,10 @@
         <v>79</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1674,7 +1674,7 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1691,10 +1691,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1720,10 +1720,10 @@
         <v>79</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1774,7 +1774,7 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1820,10 +1820,10 @@
         <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1874,7 +1874,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1891,10 +1891,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1920,10 +1920,10 @@
         <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1974,7 +1974,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -1991,10 +1991,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2017,7 +2017,7 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>103</v>
@@ -2074,7 +2074,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="104">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -328,16 +328,6 @@
   </si>
   <si>
     <t>INSTITUTION (-3)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.provider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Provider441)
-</t>
-  </si>
-  <si>
-    <t>PROVIDER (-2600)</t>
   </si>
 </sst>
 </file>
@@ -639,7 +629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.5234375" customWidth="true" bestFit="true"/>
@@ -652,7 +642,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="57.09765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="56.421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2089,106 +2079,6 @@
         <v>72</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="106">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -328,6 +328,12 @@
   </si>
   <si>
     <t>INSTITUTION (-3)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.principalClinc</t>
+  </si>
+  <si>
+    <t>PRINCIPAL CLINC (-1916)</t>
   </si>
 </sst>
 </file>
@@ -629,7 +635,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.5234375" customWidth="true" bestFit="true"/>
@@ -2079,6 +2085,106 @@
         <v>72</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -330,10 +330,10 @@
     <t>INSTITUTION (-3)</t>
   </si>
   <si>
-    <t>HospitalLocation44.principalClinc</t>
-  </si>
-  <si>
-    <t>PRINCIPAL CLINC (-1916)</t>
+    <t>HospitalLocation44.principalClinic</t>
+  </si>
+  <si>
+    <t>PRINCIPAL CLINIC (-1916)</t>
   </si>
 </sst>
 </file>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,7 +247,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>HospitalLocation44.service</t>
+    <t>HospitalLocation44.type</t>
   </si>
   <si>
     <t>1</t>
@@ -257,24 +257,6 @@
 </t>
   </si>
   <si>
-    <t>SERVICE (-9)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.stopCodeNumber</t>
-  </si>
-  <si>
-    <t>STOP CODE NUMBER (-8)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.creditStopCode</t>
-  </si>
-  <si>
-    <t>CREDIT STOP CODE (-2503)</t>
-  </si>
-  <si>
-    <t>HospitalLocation44.type</t>
-  </si>
-  <si>
     <t>TYPE (-2)</t>
   </si>
   <si>
@@ -328,6 +310,24 @@
   </si>
   <si>
     <t>INSTITUTION (-3)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.service</t>
+  </si>
+  <si>
+    <t>SERVICE (-9)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.stopCodeNumber</t>
+  </si>
+  <si>
+    <t>STOP CODE NUMBER (-8)</t>
+  </si>
+  <si>
+    <t>HospitalLocation44.creditStopCode</t>
+  </si>
+  <si>
+    <t>CREDIT STOP CODE (-2503)</t>
   </si>
   <si>
     <t>HospitalLocation44.principalClinic</t>
@@ -1713,13 +1713,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1816,10 +1816,10 @@
         <v>79</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1870,7 +1870,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>73</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -1916,10 +1916,10 @@
         <v>79</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -1970,7 +1970,7 @@
         <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>73</v>
@@ -1987,10 +1987,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2013,7 +2013,7 @@
         <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>103</v>
@@ -2070,7 +2070,7 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-HospitalLocation44.xlsx
+++ b/docs/StructureDefinition-HospitalLocation44.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
